--- a/docs/content-templates/06_lesson_resources_template.xlsx
+++ b/docs/content-templates/06_lesson_resources_template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="97">
   <si>
     <t>06 — نموذج موارد الدرس</t>
   </si>
@@ -32,12 +32,24 @@
     <t>— الأعمدة —</t>
   </si>
   <si>
+    <t>subject_code *</t>
+  </si>
+  <si>
+    <t>ملاحظة: إلزامي — يحدد المادة التي ينتمي إليها lesson_code — مثال: phys-g10-aden</t>
+  </si>
+  <si>
     <t>lesson_code *</t>
   </si>
   <si>
     <t>مثال: phys-g10-u1-l1</t>
   </si>
   <si>
+    <t>resource_code *</t>
+  </si>
+  <si>
+    <t>ملاحظة: هوية ثابتة للمورد — لا تغيّرها بين الدفعات — مثال: RES-PHYS-G10-U1-L1-01</t>
+  </si>
+  <si>
     <t>resource_type *</t>
   </si>
   <si>
@@ -56,10 +68,10 @@
     <t>مثال: فيديو YouTube تعليمي</t>
   </si>
   <si>
-    <t>resource_url</t>
-  </si>
-  <si>
-    <t>ملاحظة: رابط خارجي أو embed رسمي — مثال: https://www.youtube.com/watch?v=example</t>
+    <t>resource_url *</t>
+  </si>
+  <si>
+    <t>ملاحظة: إلزامي — رابط خارجي أو embed رسمي — مثال: https://www.youtube.com/watch?v=example</t>
   </si>
   <si>
     <t>resource_format</t>
@@ -149,9 +161,15 @@
     <t>⚠️ أي مورد خارجي: احترم الترخيص ولا تحذف attribution إلا إذا كان الترخيص يسمح بذلك.</t>
   </si>
   <si>
+    <t>phys-g10-aden</t>
+  </si>
+  <si>
     <t>phys-g10-u1-l1</t>
   </si>
   <si>
+    <t>RES-PHYS-G10-U1-L1-01</t>
+  </si>
+  <si>
     <t>video</t>
   </si>
   <si>
@@ -182,6 +200,9 @@
     <t>رابط خارجي — تحقق من حقوق النشر</t>
   </si>
   <si>
+    <t>RES-PHYS-G10-U1-L1-02</t>
+  </si>
+  <si>
     <t>mindmap</t>
   </si>
   <si>
@@ -209,6 +230,9 @@
     <t>ملف HTML محلي — RTL وجوال</t>
   </si>
   <si>
+    <t>RES-PHYS-G10-U1-L1-03</t>
+  </si>
+  <si>
     <t>experiment</t>
   </si>
   <si>
@@ -233,6 +257,9 @@
     <t>embed الرابط الرسمي فقط</t>
   </si>
   <si>
+    <t>RES-PHYS-G10-U1-L1-04</t>
+  </si>
+  <si>
     <t>pdf</t>
   </si>
   <si>
@@ -252,6 +279,9 @@
   </si>
   <si>
     <t>يُرفع الملف لاحقاً عبر لوحة الإدارة</t>
+  </si>
+  <si>
+    <t>RES-PHYS-G10-U1-L1-05</t>
   </si>
   <si>
     <t>link</t>
@@ -670,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -807,97 +837,113 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B19" t="s">
         <v>33</v>
       </c>
-      <c r="B21" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="B20" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -908,25 +954,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="21" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="19" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="4" width="21" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="21" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="19" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -966,214 +1013,250 @@
       <c r="M1" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>49</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B3" t="s">
         <v>50</v>
       </c>
-      <c r="G2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3" t="s">
+        <v>69</v>
+      </c>
+      <c r="N3" t="s">
+        <v>70</v>
+      </c>
+      <c r="O3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4" t="s">
+        <v>78</v>
+      </c>
+      <c r="N4" t="s">
+        <v>79</v>
+      </c>
+      <c r="O4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5" t="s">
+        <v>86</v>
+      </c>
+      <c r="N5" t="s">
+        <v>87</v>
+      </c>
+      <c r="O5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" t="s">
         <v>56</v>
       </c>
-      <c r="C3" t="s">
+      <c r="I6" t="s">
         <v>57</v>
       </c>
-      <c r="D3" t="s">
+      <c r="J6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" t="s">
         <v>58</v>
       </c>
-      <c r="E3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3" t="s">
-        <v>62</v>
-      </c>
-      <c r="L3" t="s">
-        <v>63</v>
-      </c>
-      <c r="M3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" t="s">
-        <v>61</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" t="s">
-        <v>71</v>
-      </c>
-      <c r="M4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5" t="s">
-        <v>77</v>
-      </c>
-      <c r="L5" t="s">
-        <v>78</v>
-      </c>
-      <c r="M5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" t="s">
-        <v>52</v>
-      </c>
-      <c r="J6">
+      <c r="L6">
         <v>5</v>
       </c>
-      <c r="K6" t="s">
-        <v>84</v>
-      </c>
-      <c r="L6" t="s">
-        <v>85</v>
-      </c>
       <c r="M6" t="s">
-        <v>86</v>
+        <v>94</v>
+      </c>
+      <c r="N6" t="s">
+        <v>95</v>
+      </c>
+      <c r="O6" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:O1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
